--- a/docs/test runs.xlsx
+++ b/docs/test runs.xlsx
@@ -5,10 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Amounts" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="WER" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="CER" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Transcript_ratio" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="24">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -84,19 +88,31 @@
   <si>
     <t xml:space="preserve">whisper_tiny</t>
   </si>
+  <si>
+    <t xml:space="preserve">Average WER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average CER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average transcript ratio</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -112,6 +128,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -156,8 +177,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -170,7 +203,1791 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFB3B3B3"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFDDDDDD"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFD320"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF420E"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF004586"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>WER!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average WER</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>WER!$A$2:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>huggingface_whisper_large_v3_czech</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>huggingface_whisper_medium_czech</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>whisper_large</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>speech_recognition_groq</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>faster_whisper_large_float16_cuda</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>faster_whisper_medium_float16_cuda</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>whisper_medium</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>speech_recognition_google</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>whisper_small</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>speech_recognition_vosk</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>whisper_base</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>whisper_tiny</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>WER!$B$2:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.0634760418801414</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.116688142120845</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.165530059136839</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.190445576047138</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.211231963903999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.26361342183346</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.285377168827284</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.45359444074635</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.464121922760283</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.493553444510357</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.511156568105951</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.52931151850311</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.63761199118342</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.758190761753475</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.926234460924431</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="100"/>
+        <c:overlap val="0"/>
+        <c:axId val="53474620"/>
+        <c:axId val="84242317"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="53474620"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="84242317"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="84242317"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="53474620"/>
+        <c:crossesAt val="1"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="dddddd"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>CER!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average CER</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:invertIfNegative val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:txPr>
+                <a:bodyPr wrap="none"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                      <a:uFillTx/>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator> </c:separator>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>CER!$A$2:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>huggingface_whisper_large_v3_czech</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>huggingface_whisper_medium_czech</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>whisper_large</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>speech_recognition_groq</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>faster_whisper_large_float16_cuda</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>faster_whisper_medium_float16_cuda</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>whisper_medium</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>speech_recognition_google</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>speech_recognition_vosk</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>whisper_small</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>whisper_base</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>whisper_tiny</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>CER!$B$2:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.0147280820944806</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0278402638358035</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0440938281502985</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.0535375276071712</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.0581072165114405</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.0716067171792048</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.0824529863589437</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.102972938151722</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.109204969775619</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.112540134117956</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.141557801094054</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.141815069459032</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.156725165271304</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.279014130933508</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.402814787294407</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="100"/>
+        <c:overlap val="0"/>
+        <c:axId val="54732237"/>
+        <c:axId val="10342075"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="54732237"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="10342075"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="10342075"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="54732237"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="dddddd"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Transcript_ratio!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average transcript ratio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffd320"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Transcript_ratio!$A$2:$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>whisper_base</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>whisper_small</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>whisper_tiny</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>speech_recognition_vosk</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>whisper_medium</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>faster_whisper_medium_float16_cuda</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>faster_whisper_large_float16_cuda</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>speech_recognition_google</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>huggingface_whisper_large_v3_czech</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>huggingface_whisper_medium_czech</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Transcript_ratio!$B$2:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.0441173506620093</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.058864187630119</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0737053906193861</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.0932991636551523</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.111690524931908</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.121666608441389</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.130435018511475</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.136177451289278</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.153283050739494</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.228220963777834</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.256016071870918</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.285522869842013</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.795146019510512</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="100"/>
+        <c:overlap val="0"/>
+        <c:axId val="34517594"/>
+        <c:axId val="407117"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="34517594"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="407117"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="407117"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="34517594"/>
+        <c:crossesAt val="1"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="dddddd"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average WER</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$A$2:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>huggingface_whisper_large_v3_czech</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>huggingface_whisper_medium_czech</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>whisper_large</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>speech_recognition_groq</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>faster_whisper_large_float16_cuda</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>faster_whisper_medium_float16_cuda</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>whisper_medium</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>speech_recognition_google</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>whisper_small</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>speech_recognition_vosk</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>whisper_base</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>whisper_tiny</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$B$2:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.0634760418801414</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.116688142120845</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.165530059136839</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.190445576047138</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.211231963903999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.26361342183346</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.285377168827284</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.45359444074635</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.464121922760283</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.493553444510357</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.511156568105951</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.52931151850311</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.63761199118342</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.758190761753475</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.926234460924431</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average CER</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$A$2:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>huggingface_whisper_large_v3_czech</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>huggingface_whisper_medium_czech</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>whisper_large</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>speech_recognition_groq</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>faster_whisper_large_float16_cuda</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>faster_whisper_medium_float16_cuda</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>whisper_medium</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>speech_recognition_google</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>whisper_small</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>speech_recognition_vosk</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>whisper_base</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>whisper_tiny</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$C$2:$C$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.0147280820944806</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0278402638358035</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0440938281502985</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.0535375276071712</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.0581072165114405</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.0716067171792048</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.0824529863589437</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.112540134117956</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.141815069459032</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.102972938151722</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.109204969775619</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.141557801094054</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.156725165271304</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.279014130933508</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.402814787294407</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average transcript ratio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffd320"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$A$2:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>huggingface_whisper_large_v3_czech</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>huggingface_whisper_medium_czech</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>whisper_large</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>speech_recognition_groq</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>faster_whisper_large_float16_cuda</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>faster_whisper_medium_float16_cuda</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>whisper_medium</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>speech_recognition_google</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>whisper_small</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>speech_recognition_vosk</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>whisper_base</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>whisper_tiny</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$D$2:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.256016071870918</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.795146019510512</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.153283050739494</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.136177451289278</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.130435018511475</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.228220963777834</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.0737053906193861</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.285522869842013</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.121666608441389</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.111690524931908</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.0441173506620093</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.058864187630119</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.0932991636551523</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="100"/>
+        <c:overlap val="0"/>
+        <c:axId val="14642597"/>
+        <c:axId val="94186407"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="14642597"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="94186407"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="94186407"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="14642597"/>
+        <c:crossesAt val="1"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="dddddd"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3600</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>803880</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>124200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4994640" y="163080"/>
+        <a:ext cx="6285960" cy="3212280"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>720</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>771840</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>124560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4981680" y="172080"/>
+        <a:ext cx="6256800" cy="3203640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2160</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>160920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>781920</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>149400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="5483520" y="160920"/>
+        <a:ext cx="6265440" cy="3239640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>25920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>176400</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>59040</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6948720" y="188640"/>
+        <a:ext cx="9884520" cy="5559840"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -287,239 +2104,239 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="37.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="B2" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="B3" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="B4" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="B5" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="B6" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="B7" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C8" s="0" t="n">
+      <c r="B8" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>10187</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="B9" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>476</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>2722</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>1794</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="B11" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="B12" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>3072</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>3329</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>3001</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="B14" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C15" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D15" s="0" t="n">
+      <c r="B15" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C16" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D16" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E16" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F16" s="0" t="n">
+      <c r="B16" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F16" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -532,4 +2349,782 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="20.17"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0.0634760418801414</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0.116688142120845</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0.165530059136839</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.190445576047138</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.211231963903999</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.26361342183346</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.285377168827284</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0.45359444074635</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.464121922760283</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0.493553444510357</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.511156568105951</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.52931151850311</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.63761199118342</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0.758190761753475</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0.926234460924431</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="20.17"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0.0147280820944806</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0.0278402638358035</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0.0440938281502985</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.0535375276071712</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0.0581072165114405</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.0716067171792048</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.0824529863589437</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0.102972938151722</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.109204969775619</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0.112540134117956</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.141557801094054</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.141815069459032</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.156725165271304</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0.279014130933508</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0.402814787294407</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="20.17"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0.0441173506620093</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0.058864187630119</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0.0737053906193861</v>
+      </c>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.0932991636551523</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.111690524931908</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.121666608441389</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.130435018511475</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0.136177451289278</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.153283050739494</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0.228220963777834</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.256016071870918</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.285522869842013</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.795146019510512</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2.13081619568869</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>4.11859599274385</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="20.17"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0.0634760418801414</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.0147280820944806</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.256016071870918</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0.116688142120845</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.0278402638358035</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.795146019510512</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0.165530059136839</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.0440938281502985</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.190445576047138</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.0535375276071712</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.211231963903999</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.0581072165114405</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.153283050739494</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.26361342183346</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0.0716067171792048</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.136177451289278</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.285377168827284</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0.0824529863589437</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.130435018511475</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0.45359444074635</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0.112540134117956</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.228220963777834</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.464121922760283</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0.141815069459032</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.0737053906193861</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0.493553444510357</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0.102972938151722</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.285522869842013</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.511156568105951</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0.109204969775619</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.121666608441389</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.52931151850311</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0.141557801094054</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.111690524931908</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.63761199118342</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0.156725165271304</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.0441173506620093</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0.758190761753475</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>0.279014130933508</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.058864187630119</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0.926234460924431</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0.402814787294407</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.0932991636551523</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/test runs.xlsx
+++ b/docs/test runs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Amounts" sheetId="1" state="visible" r:id="rId3"/>
@@ -102,12 +102,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -128,6 +130,29 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC9211E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -177,7 +202,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -186,12 +211,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -203,10 +236,18 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC9211E"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -223,7 +264,7 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF18A303"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -236,7 +277,7 @@
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF0369A3"/>
       <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -259,14 +300,14 @@
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFD320"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF420E"/>
+      <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF004586"/>
+      <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFC9211E"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -280,10 +321,51 @@
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Porovnanie modelov podľa WER</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.476575028636884"/>
+          <c:y val="0.142961219457521"/>
+          <c:w val="0.495189003436426"/>
+          <c:h val="0.711611746245237"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
-        <c:barDir val="col"/>
+        <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -302,7 +384,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="004586"/>
+              <a:srgbClr val="18a303"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -316,12 +398,17 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -359,34 +446,34 @@
                   <c:v>whisper_large</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>speech_recognition_google</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>speech_recognition_groq</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>faster_whisper_large_float16_cuda</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
+                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>speech_recognition_vosk</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>faster_whisper_medium_float16_cuda</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>whisper_medium</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>speech_recognition_google</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
+                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>whisper_small</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>speech_recognition_vosk</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>whisper_base</c:v>
@@ -401,52 +488,52 @@
             <c:numRef>
               <c:f>WER!$B$2:$B$16</c:f>
               <c:numCache>
-                <c:formatCode>0.000000</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.0634760418801414</c:v>
+                  <c:v>0.0441468721692524</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.116688142120845</c:v>
+                  <c:v>0.0914443287122927</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.165530059136839</c:v>
+                  <c:v>0.112411016667618</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.190445576047138</c:v>
+                  <c:v>0.119678415800646</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.211231963903999</c:v>
+                  <c:v>0.137222644731534</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.26361342183346</c:v>
+                  <c:v>0.140363740121024</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.285377168827284</c:v>
+                  <c:v>0.157541755617472</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.45359444074635</c:v>
+                  <c:v>0.164664052820296</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.464121922760283</c:v>
+                  <c:v>0.174985413000473</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.493553444510357</c:v>
+                  <c:v>0.212571002672446</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.511156568105951</c:v>
+                  <c:v>0.236012416163012</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.52931151850311</c:v>
+                  <c:v>0.395130170015131</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.63761199118342</c:v>
+                  <c:v>0.418928020613512</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.758190761753475</c:v>
+                  <c:v>0.732145359088816</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.926234460924431</c:v>
+                  <c:v>0.908138646571831</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -454,17 +541,47 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="53474620"/>
-        <c:axId val="84242317"/>
+        <c:axId val="76714135"/>
+        <c:axId val="75039707"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="53474620"/>
+        <c:axId val="76714135"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>Model</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -481,13 +598,17 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84242317"/>
+        <c:crossAx val="75039707"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -495,7 +616,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84242317"/>
+        <c:axId val="75039707"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -510,7 +631,37 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.000" sourceLinked="0"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>Priemerný WER</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -527,15 +678,19 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53474620"/>
+        <c:crossAx val="76714135"/>
         <c:crossesAt val="1"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -546,28 +701,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-              <a:uFillTx/>
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -587,10 +720,51 @@
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Porovnanie modelov podľa CER</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.476547734952179"/>
+          <c:y val="0.142889162837611"/>
+          <c:w val="0.495160643720291"/>
+          <c:h val="0.711531995965482"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
-        <c:barDir val="col"/>
+        <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -609,59 +783,31 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ff420e"/>
+              <a:srgbClr val="0369a3"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="9"/>
-            <c:invertIfNegative val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="ff420e"/>
-              </a:solidFill>
-              <a:ln w="0">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
           <c:dLbls>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:txPr>
-                <a:bodyPr wrap="none"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator> </c:separator>
-            </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -696,37 +842,37 @@
                   <c:v>huggingface_whisper_medium_czech</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>whisper_large</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
+                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>speech_recognition_groq</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
+                  <c:v>speech_recognition_google</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>faster_whisper_large_float16_cuda</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>faster_whisper_medium_float16_cuda</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
+                  <c:v>speech_recognition_vosk</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>whisper_medium</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>speech_recognition_google</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>speech_recognition_vosk</c:v>
-                </c:pt>
                 <c:pt idx="11">
+                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>whisper_small</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>whisper_base</c:v>
@@ -744,49 +890,49 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.0147280820944806</c:v>
+                  <c:v>0.0108465551141083</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0278402638358035</c:v>
+                  <c:v>0.0226342666643933</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0440938281502985</c:v>
+                  <c:v>0.027455556100141</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0535375276071712</c:v>
+                  <c:v>0.0332052892550728</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0581072165114405</c:v>
+                  <c:v>0.034608729144128</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0716067171792048</c:v>
+                  <c:v>0.0415494509686245</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0824529863589437</c:v>
+                  <c:v>0.0460638599643128</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.102972938151722</c:v>
+                  <c:v>0.0463268620757961</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.109204969775619</c:v>
+                  <c:v>0.0599086107996893</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.112540134117956</c:v>
+                  <c:v>0.0629669593903209</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.141557801094054</c:v>
+                  <c:v>0.0711634580873181</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.141815069459032</c:v>
+                  <c:v>0.083912055247766</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.156725165271304</c:v>
+                  <c:v>0.131130033920739</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.279014130933508</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.402814787294407</c:v>
+                  <c:v>0.396456691370473</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -794,16 +940,46 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="54732237"/>
-        <c:axId val="10342075"/>
+        <c:axId val="52307051"/>
+        <c:axId val="42555643"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54732237"/>
+        <c:axId val="52307051"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>Model</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -821,13 +997,17 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10342075"/>
+        <c:crossAx val="42555643"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -835,9 +1015,10 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10342075"/>
+        <c:axId val="42555643"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -850,7 +1031,37 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>Priemerný CER</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -867,15 +1078,19 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54732237"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossAx val="52307051"/>
+        <c:crossesAt val="1"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -886,28 +1101,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-              <a:uFillTx/>
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -927,10 +1120,51 @@
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Rýchlosť prepisu modelov</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.441734090085738"/>
+          <c:y val="0.140777843252799"/>
+          <c:w val="0.492452602342712"/>
+          <c:h val="0.650677666470242"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
-        <c:barDir val="col"/>
+        <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -963,12 +1197,17 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1089,17 +1328,47 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="34517594"/>
-        <c:axId val="407117"/>
+        <c:axId val="35513244"/>
+        <c:axId val="52684829"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="34517594"/>
+        <c:axId val="35513244"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>Model</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1116,13 +1385,17 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="407117"/>
+        <c:crossAx val="52684829"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1130,7 +1403,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="407117"/>
+        <c:axId val="52684829"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1145,6 +1418,44 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>Sekundy spracovania na 1 sekundu audia</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.44539032783916"/>
+              <c:y val="0.884869196323356"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
         <c:numFmt formatCode="0.000" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -1162,15 +1473,19 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34517594"/>
+        <c:crossAx val="35513244"/>
         <c:crossesAt val="1"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1181,28 +1496,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-              <a:uFillTx/>
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -1222,10 +1515,59 @@
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Porovnanie modelov podľa WER a CER</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.28455843469064"/>
+          <c:y val="0.0163224516988674"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.441535776614311"/>
+          <c:y val="0.118933925596891"/>
+          <c:w val="0.370299857210852"/>
+          <c:h val="0.724486396446419"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
-        <c:barDir val="col"/>
+        <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -1244,7 +1586,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="004586"/>
+              <a:srgbClr val="18a303"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -1301,34 +1643,34 @@
                   <c:v>whisper_large</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>speech_recognition_google</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>speech_recognition_groq</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>faster_whisper_large_float16_cuda</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
+                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>speech_recognition_vosk</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>faster_whisper_medium_float16_cuda</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>whisper_medium</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>speech_recognition_google</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
+                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>whisper_small</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>speech_recognition_vosk</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>whisper_base</c:v>
@@ -1346,49 +1688,49 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.0634760418801414</c:v>
+                  <c:v>0.0441468721692524</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.116688142120845</c:v>
+                  <c:v>0.0914443287122927</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.165530059136839</c:v>
+                  <c:v>0.112411016667618</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.190445576047138</c:v>
+                  <c:v>0.119678415800646</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.211231963903999</c:v>
+                  <c:v>0.137222644731534</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.26361342183346</c:v>
+                  <c:v>0.140363740121024</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.285377168827284</c:v>
+                  <c:v>0.157541755617472</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.45359444074635</c:v>
+                  <c:v>0.164664052820296</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.464121922760283</c:v>
+                  <c:v>0.174985413000473</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.493553444510357</c:v>
+                  <c:v>0.212571002672446</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.511156568105951</c:v>
+                  <c:v>0.236012416163012</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.52931151850311</c:v>
+                  <c:v>0.395130170015131</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.63761199118342</c:v>
+                  <c:v>0.418928020613512</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.758190761753475</c:v>
+                  <c:v>0.732145359088816</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.926234460924431</c:v>
+                  <c:v>0.908138646571831</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1410,7 +1752,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ff420e"/>
+              <a:srgbClr val="0369a3"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -1467,34 +1809,34 @@
                   <c:v>whisper_large</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>speech_recognition_google</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>speech_recognition_groq</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>faster_whisper_large_float16_cuda</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
+                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>speech_recognition_vosk</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>faster_whisper_medium_float16_cuda</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
                   <c:v>whisper_medium</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>speech_recognition_google</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
+                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>whisper_small</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>speech_recognition_vosk</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>whisper_base</c:v>
@@ -1512,209 +1854,49 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.0147280820944806</c:v>
+                  <c:v>0.0108465551141083</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0278402638358035</c:v>
+                  <c:v>0.0226342666643933</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0440938281502985</c:v>
+                  <c:v>0.0332052892550728</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0535375276071712</c:v>
+                  <c:v>0.0460638599643128</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0581072165114405</c:v>
+                  <c:v>0.027455556100141</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0716067171792048</c:v>
+                  <c:v>0.0415494509686245</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0824529863589437</c:v>
+                  <c:v>0.0463268620757961</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.112540134117956</c:v>
+                  <c:v>0.034608729144128</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.141815069459032</c:v>
+                  <c:v>0.0629669593903209</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.102972938151722</c:v>
+                  <c:v>0.0599086107996893</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.109204969775619</c:v>
+                  <c:v>0.0711634580873181</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.141557801094054</c:v>
+                  <c:v>0.083912055247766</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.156725165271304</c:v>
+                  <c:v>0.131130033920739</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.279014130933508</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.402814787294407</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Summary!$D$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Average transcript ratio</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ffd320"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Summary!$A$2:$A$16</c:f>
-              <c:strCache>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>huggingface_whisper_large_v3_czech</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>huggingface_whisper_medium_czech</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>whisper_large</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>speech_recognition_groq</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>faster_whisper_large_float16_cuda</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>faster_whisper_medium_float16_cuda</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>whisper_medium</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>speech_recognition_google</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>whisper_small</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>speech_recognition_vosk</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>whisper_base</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>whisper_tiny</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Summary!$D$2:$D$16</c:f>
-              <c:numCache>
-                <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>0.256016071870918</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.795146019510512</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.153283050739494</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.136177451289278</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.130435018511475</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.228220963777834</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.0737053906193861</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.285522869842013</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.121666608441389</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.111690524931908</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.0441173506620093</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.058864187630119</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.0932991636551523</c:v>
+                  <c:v>0.396456691370473</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1722,16 +1904,46 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="14642597"/>
-        <c:axId val="94186407"/>
+        <c:axId val="45937911"/>
+        <c:axId val="9442405"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="14642597"/>
+        <c:axId val="45937911"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>Model</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -1755,7 +1967,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94186407"/>
+        <c:crossAx val="9442405"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1763,7 +1975,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94186407"/>
+        <c:axId val="9442405"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1778,7 +1990,37 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.000" sourceLinked="0"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>WER a CER</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1801,9 +2043,9 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14642597"/>
+        <c:crossAx val="45937911"/>
         <c:crossesAt val="1"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1861,9 +2103,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>803880</xdr:colOff>
+      <xdr:colOff>803520</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>124200</xdr:rowOff>
+      <xdr:rowOff>123840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1872,7 +2114,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4994640" y="163080"/>
-        <a:ext cx="6285960" cy="3212280"/>
+        <a:ext cx="6285600" cy="3211920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1890,15 +2132,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>720</xdr:colOff>
+      <xdr:colOff>3600</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:rowOff>360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>771840</xdr:colOff>
+      <xdr:colOff>803520</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>124560</xdr:rowOff>
+      <xdr:rowOff>123840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1906,8 +2148,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4981680" y="172080"/>
-        <a:ext cx="6256800" cy="3203640"/>
+        <a:off x="4994640" y="163080"/>
+        <a:ext cx="6285600" cy="3211920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1925,15 +2167,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2160</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>160920</xdr:rowOff>
+      <xdr:colOff>4320</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>781920</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>149400</xdr:rowOff>
+      <xdr:colOff>480960</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>128520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1941,8 +2183,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5483520" y="160920"/>
-        <a:ext cx="6265440" cy="3239640"/>
+        <a:off x="5485680" y="162720"/>
+        <a:ext cx="5962320" cy="3054600"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1959,16 +2201,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>45720</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>25920</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>39960</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>176400</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>59040</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>28800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1976,8 +2218,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6948720" y="188640"/>
-        <a:ext cx="9884520" cy="5559840"/>
+        <a:off x="5521320" y="38160"/>
+        <a:ext cx="6807240" cy="3241800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2360,8 +2602,8 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="20.17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2371,8 +2613,6 @@
       <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
@@ -2381,150 +2621,150 @@
         <v>11</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.0634760418801414</v>
+        <v>0.0441468721692524</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="2"/>
+      <c r="D2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.116688142120845</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+        <v>0.0914443287122927</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.165530059136839</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+        <v>0.112411016667618</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.190445576047138</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+        <v>0.119678415800646</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.211231963903999</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+        <v>0.137222644731534</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.26361342183346</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+        <v>0.140363740121024</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.285377168827284</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+        <v>0.157541755617472</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.45359444074635</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+        <v>0.164664052820296</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.464121922760283</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+        <v>0.174985413000473</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.493553444510357</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+        <v>0.212571002672446</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.511156568105951</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+        <v>0.236012416163012</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.52931151850311</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+        <v>0.395130170015131</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.63761199118342</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+        <v>0.418928020613512</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.758190761753475</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+        <v>0.732145359088816</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.926234460924431</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+        <v>0.908138646571831</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
@@ -2549,8 +2789,8 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="20.17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2560,7 +2800,7 @@
       <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="C1" s="0"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
@@ -2568,136 +2808,151 @@
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>0.0147280820944806</v>
-      </c>
-      <c r="D2" s="2"/>
+      <c r="B2" s="4" t="n">
+        <v>0.0108465551141083</v>
+      </c>
+      <c r="C2" s="0"/>
+      <c r="D2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>0.0278402638358035</v>
-      </c>
-      <c r="D3" s="2"/>
+      <c r="B3" s="4" t="n">
+        <v>0.0226342666643933</v>
+      </c>
+      <c r="C3" s="0"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>0.0440938281502985</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>0.027455556100141</v>
+      </c>
+      <c r="C4" s="0"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>0.0535375276071712</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>0.0332052892550728</v>
+      </c>
+      <c r="C5" s="0"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0.0581072165114405</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0.034608729144128</v>
+      </c>
+      <c r="C6" s="0"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0.0716067171792048</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>0.0415494509686245</v>
+      </c>
+      <c r="C7" s="0"/>
+      <c r="D7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>0.0824529863589437</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>0.0460638599643128</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>0.102972938151722</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0.0463268620757961</v>
+      </c>
+      <c r="C9" s="0"/>
+      <c r="D9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>0.109204969775619</v>
-      </c>
-      <c r="D10" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>0.0599086107996893</v>
+      </c>
+      <c r="C10" s="0"/>
+      <c r="D10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0.112540134117956</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>0.0629669593903209</v>
+      </c>
+      <c r="C11" s="0"/>
+      <c r="D11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>0.141557801094054</v>
-      </c>
-      <c r="D12" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>0.0711634580873181</v>
+      </c>
+      <c r="C12" s="0"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0.141815069459032</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>0.083912055247766</v>
+      </c>
+      <c r="C13" s="0"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>0.156725165271304</v>
-      </c>
-      <c r="D14" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0.131130033920739</v>
+      </c>
+      <c r="C14" s="0"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="4" t="n">
         <v>0.279014130933508</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="C15" s="0"/>
+      <c r="D15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>0.402814787294407</v>
-      </c>
-      <c r="D16" s="2"/>
+      <c r="B16" s="4" t="n">
+        <v>0.396456691370473</v>
+      </c>
+      <c r="C16" s="0"/>
+      <c r="D16" s="4"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
@@ -2722,7 +2977,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="20.17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2732,7 +2987,6 @@
       <c r="B1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
@@ -2740,7 +2994,7 @@
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="4" t="n">
         <v>0.0441173506620093</v>
       </c>
       <c r="C2" s="3"/>
@@ -2749,127 +3003,127 @@
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="4" t="n">
         <v>0.058864187630119</v>
       </c>
-      <c r="C3" s="2"/>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="4" t="n">
         <v>0.0737053906193861</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="4" t="n">
         <v>0.0932991636551523</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="4" t="n">
         <v>0.111690524931908</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="4" t="n">
         <v>0.121666608441389</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="4" t="n">
         <v>0.130435018511475</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="4" t="n">
         <v>0.136177451289278</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="4" t="n">
         <v>0.153283050739494</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="C10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="4" t="n">
         <v>0.228220963777834</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="4" t="n">
         <v>0.256016071870918</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="4" t="n">
         <v>0.285522869842013</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="4" t="n">
         <v>0.795146019510512</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="4" t="n">
         <v>2.13081619568869</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="4" t="n">
         <v>4.11859599274385</v>
       </c>
-      <c r="C16" s="2"/>
+      <c r="C16" s="4"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
@@ -2890,11 +3144,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="20.17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2915,13 +3169,13 @@
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>0.0634760418801414</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.0147280820944806</v>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="B2" s="4" t="n">
+        <v>0.0441468721692524</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>0.0108465551141083</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>0.256016071870918</v>
       </c>
     </row>
@@ -2929,13 +3183,13 @@
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>0.116688142120845</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0.0278402638358035</v>
-      </c>
-      <c r="D3" s="2" t="n">
+      <c r="B3" s="4" t="n">
+        <v>0.0914443287122927</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>0.0226342666643933</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>0.795146019510512</v>
       </c>
     </row>
@@ -2943,163 +3197,167 @@
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>0.165530059136839</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.0440938281502985</v>
-      </c>
-      <c r="D4" s="2"/>
+      <c r="B4" s="4" t="n">
+        <v>0.112411016667618</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>0.0332052892550728</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.13081619568869</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>0.190445576047138</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0.0535375276071712</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>0.119678415800646</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0.0460638599643128</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.228220963777834</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>0.211231963903999</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0.0581072165114405</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.153283050739494</v>
+        <v>10</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0.137222644731534</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0.027455556100141</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.285522869842013</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0.26361342183346</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0.0716067171792048</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.136177451289278</v>
+        <v>14</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>0.140363740121024</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0.0415494509686245</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4.11859599274385</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>0.285377168827284</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>0.0824529863589437</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0.130435018511475</v>
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>0.157541755617472</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.0463268620757961</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.153283050739494</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>0.45359444074635</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>0.112540134117956</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.228220963777834</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>0.164664052820296</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0.034608729144128</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.121666608441389</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>0.464121922760283</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0.141815069459032</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0.0737053906193861</v>
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>0.174985413000473</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0.0629669593903209</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0.111690524931908</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0.493553444510357</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0.102972938151722</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0.285522869842013</v>
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>0.212571002672446</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0.0599086107996893</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.136177451289278</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>0.511156568105951</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>0.109204969775619</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0.121666608441389</v>
+        <v>18</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>0.236012416163012</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0.0711634580873181</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0.130435018511475</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0.52931151850311</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>0.141557801094054</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>0.111690524931908</v>
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>0.395130170015131</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0.083912055247766</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.0441173506620093</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>0.63761199118342</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>0.156725165271304</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0.0441173506620093</v>
+        <v>19</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0.418928020613512</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>0.131130033920739</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.0737053906193861</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>0.758190761753475</v>
-      </c>
-      <c r="C15" s="2" t="n">
+      <c r="B15" s="4" t="n">
+        <v>0.732145359088816</v>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>0.279014130933508</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="4" t="n">
         <v>0.058864187630119</v>
       </c>
     </row>
@@ -3107,15 +3365,60 @@
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>0.926234460924431</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>0.402814787294407</v>
-      </c>
-      <c r="D16" s="2" t="n">
+      <c r="B16" s="4" t="n">
+        <v>0.908138646571831</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0.396456691370473</v>
+      </c>
+      <c r="D16" s="4" t="n">
         <v>0.0932991636551523</v>
       </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="4"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="4"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="4"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="4"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/test runs.xlsx
+++ b/docs/test runs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Amounts" sheetId="1" state="visible" r:id="rId3"/>
@@ -133,6 +133,7 @@
     </font>
     <font>
       <sz val="13"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -144,8 +145,16 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -153,11 +162,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -168,12 +172,19 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -202,7 +213,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -223,8 +234,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -335,8 +362,12 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:rPr>
               <a:t>Porovnanie modelov podľa WER</a:t>
             </a:r>
@@ -359,9 +390,9 @@
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
           <c:x val="0.476575028636884"/>
-          <c:y val="0.142961219457521"/>
+          <c:y val="0.142905178211163"/>
           <c:w val="0.495189003436426"/>
-          <c:h val="0.711611746245237"/>
+          <c:h val="0.711499663752522"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -541,11 +572,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="76714135"/>
-        <c:axId val="75039707"/>
+        <c:axId val="801057"/>
+        <c:axId val="24557783"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="76714135"/>
+        <c:axId val="801057"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -565,8 +596,12 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Model</a:t>
                 </a:r>
@@ -608,7 +643,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75039707"/>
+        <c:crossAx val="24557783"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -616,7 +651,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="75039707"/>
+        <c:axId val="24557783"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -645,8 +680,12 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Priemerný WER</a:t>
                 </a:r>
@@ -688,7 +727,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76714135"/>
+        <c:crossAx val="801057"/>
         <c:crossesAt val="1"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -734,8 +773,12 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:rPr>
               <a:t>Porovnanie modelov podľa CER</a:t>
             </a:r>
@@ -757,10 +800,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.476547734952179"/>
-          <c:y val="0.142889162837611"/>
-          <c:w val="0.495160643720291"/>
-          <c:h val="0.711531995965482"/>
+          <c:x val="0.47651775486827"/>
+          <c:y val="0.142905178211163"/>
+          <c:w val="0.495131729667812"/>
+          <c:h val="0.711499663752522"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -940,11 +983,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="52307051"/>
-        <c:axId val="42555643"/>
+        <c:axId val="91668631"/>
+        <c:axId val="23656894"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="52307051"/>
+        <c:axId val="91668631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -964,8 +1007,12 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Model</a:t>
                 </a:r>
@@ -1007,7 +1054,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42555643"/>
+        <c:crossAx val="23656894"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1015,7 +1062,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42555643"/>
+        <c:axId val="23656894"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1045,8 +1092,12 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Priemerný CER</a:t>
                 </a:r>
@@ -1088,7 +1139,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52307051"/>
+        <c:crossAx val="91668631"/>
         <c:crossesAt val="1"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1134,8 +1185,12 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:rPr>
               <a:t>Rýchlosť prepisu modelov</a:t>
             </a:r>
@@ -1158,9 +1213,9 @@
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
           <c:x val="0.441734090085738"/>
-          <c:y val="0.140777843252799"/>
+          <c:y val="0.140718915733648"/>
           <c:w val="0.492452602342712"/>
-          <c:h val="0.650677666470242"/>
+          <c:h val="0.650559811431939"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -1328,11 +1383,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="35513244"/>
-        <c:axId val="52684829"/>
+        <c:axId val="94962989"/>
+        <c:axId val="14938605"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="35513244"/>
+        <c:axId val="94962989"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1352,8 +1407,12 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Model</a:t>
                 </a:r>
@@ -1395,7 +1454,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52684829"/>
+        <c:crossAx val="14938605"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1403,7 +1462,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="52684829"/>
+        <c:axId val="14938605"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1432,8 +1491,12 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Sekundy spracovania na 1 sekundu audia</a:t>
                 </a:r>
@@ -1444,8 +1507,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.44539032783916"/>
-              <c:y val="0.884869196323356"/>
+              <c:x val="0.445417220142495"/>
+              <c:y val="0.884737772539776"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -1483,7 +1546,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35513244"/>
+        <c:crossAx val="94962989"/>
         <c:crossesAt val="1"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1529,8 +1592,12 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:rPr>
               <a:t>Porovnanie modelov podľa WER a CER</a:t>
             </a:r>
@@ -1541,8 +1608,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.28455843469064"/>
-          <c:y val="0.0163224516988674"/>
+          <c:x val="0.284520598656724"/>
+          <c:y val="0.016435313714603"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1563,7 +1630,7 @@
           <c:x val="0.441535776614311"/>
           <c:y val="0.118933925596891"/>
           <c:w val="0.370299857210852"/>
-          <c:h val="0.724486396446419"/>
+          <c:h val="0.724375347029428"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -1600,12 +1667,17 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1634,49 +1706,49 @@
               <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>huggingface_whisper_large_v3_czech</c:v>
+                  <c:v>whisper_tiny</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>huggingface_whisper_medium_czech</c:v>
+                  <c:v>whisper_base</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>whisper_large</c:v>
+                  <c:v>whisper_small</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>speech_recognition_google</c:v>
+                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
+                  <c:v>whisper_medium</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>speech_recognition_groq</c:v>
+                  <c:v>faster_whisper_medium_float16_cuda</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>faster_whisper_large_float16_cuda</c:v>
+                  <c:v>speech_recognition_vosk</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>speech_recognition_vosk</c:v>
+                  <c:v>faster_whisper_large_float16_cuda</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>faster_whisper_medium_float16_cuda</c:v>
+                  <c:v>speech_recognition_groq</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>whisper_medium</c:v>
+                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
+                  <c:v>speech_recognition_google</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>whisper_small</c:v>
+                  <c:v>whisper_large</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>whisper_base</c:v>
+                  <c:v>huggingface_whisper_medium_czech</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>whisper_tiny</c:v>
+                  <c:v>huggingface_whisper_large_v3_czech</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1688,49 +1760,49 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.0441468721692524</c:v>
+                  <c:v>0.908138646571831</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0914443287122927</c:v>
+                  <c:v>0.732145359088816</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.112411016667618</c:v>
+                  <c:v>0.418928020613512</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.119678415800646</c:v>
+                  <c:v>0.395130170015131</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.137222644731534</c:v>
+                  <c:v>0.236012416163012</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.140363740121024</c:v>
+                  <c:v>0.212571002672446</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.157541755617472</c:v>
+                  <c:v>0.174985413000473</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.164664052820296</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.174985413000473</c:v>
+                  <c:v>0.157541755617472</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.212571002672446</c:v>
+                  <c:v>0.140363740121024</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.236012416163012</c:v>
+                  <c:v>0.137222644731534</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.395130170015131</c:v>
+                  <c:v>0.119678415800646</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.418928020613512</c:v>
+                  <c:v>0.112411016667618</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.732145359088816</c:v>
+                  <c:v>0.0914443287122927</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.908138646571831</c:v>
+                  <c:v>0.0441468721692524</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1766,12 +1838,17 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1800,49 +1877,49 @@
               <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>huggingface_whisper_large_v3_czech</c:v>
+                  <c:v>whisper_tiny</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>huggingface_whisper_medium_czech</c:v>
+                  <c:v>whisper_base</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>whisper_large</c:v>
+                  <c:v>whisper_small</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>speech_recognition_google</c:v>
+                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
+                  <c:v>whisper_medium</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>speech_recognition_groq</c:v>
+                  <c:v>faster_whisper_medium_float16_cuda</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>faster_whisper_large_float16_cuda</c:v>
+                  <c:v>speech_recognition_vosk</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>huggingface_wav2vec2_xlsr_53_czech</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>speech_recognition_vosk</c:v>
+                  <c:v>faster_whisper_large_float16_cuda</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>faster_whisper_medium_float16_cuda</c:v>
+                  <c:v>speech_recognition_groq</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>whisper_medium</c:v>
+                  <c:v>huggingface_wav2vec2_xlsr_czech_sammy</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>huggingface_wav2vec2_xlsr_czech</c:v>
+                  <c:v>speech_recognition_google</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>whisper_small</c:v>
+                  <c:v>whisper_large</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>whisper_base</c:v>
+                  <c:v>huggingface_whisper_medium_czech</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>whisper_tiny</c:v>
+                  <c:v>huggingface_whisper_large_v3_czech</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1854,49 +1931,49 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.0108465551141083</c:v>
+                  <c:v>0.396456691370473</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0226342666643933</c:v>
+                  <c:v>0.279014130933508</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0332052892550728</c:v>
+                  <c:v>0.131130033920739</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0460638599643128</c:v>
+                  <c:v>0.083912055247766</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.027455556100141</c:v>
+                  <c:v>0.0711634580873181</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0415494509686245</c:v>
+                  <c:v>0.0599086107996893</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0463268620757961</c:v>
+                  <c:v>0.0629669593903209</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.034608729144128</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0629669593903209</c:v>
+                  <c:v>0.0463268620757961</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.0599086107996893</c:v>
+                  <c:v>0.0415494509686245</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.0711634580873181</c:v>
+                  <c:v>0.027455556100141</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.083912055247766</c:v>
+                  <c:v>0.0460638599643128</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.131130033920739</c:v>
+                  <c:v>0.0332052892550728</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.279014130933508</c:v>
+                  <c:v>0.0226342666643933</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.396456691370473</c:v>
+                  <c:v>0.0108465551141083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1904,11 +1981,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="45937911"/>
-        <c:axId val="9442405"/>
+        <c:axId val="79824178"/>
+        <c:axId val="64841780"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="45937911"/>
+        <c:axId val="79824178"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1928,8 +2005,12 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Model</a:t>
                 </a:r>
@@ -1944,7 +2025,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1961,13 +2042,17 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9442405"/>
+        <c:crossAx val="64841780"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1975,7 +2060,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="9442405"/>
+        <c:axId val="64841780"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2004,8 +2089,12 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr sz="900" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>WER a CER</a:t>
                 </a:r>
@@ -2037,13 +2126,17 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45937911"/>
+        <c:crossAx val="79824178"/>
         <c:crossesAt val="1"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2071,8 +2164,12 @@
         <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
               <a:uFillTx/>
               <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -2103,9 +2200,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>803520</xdr:colOff>
+      <xdr:colOff>803160</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>123840</xdr:rowOff>
+      <xdr:rowOff>123480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2114,7 +2211,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4994640" y="163080"/>
-        <a:ext cx="6285600" cy="3211920"/>
+        <a:ext cx="6285240" cy="3211560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2138,9 +2235,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>803520</xdr:colOff>
+      <xdr:colOff>803160</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>123840</xdr:rowOff>
+      <xdr:rowOff>123480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2149,7 +2246,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4994640" y="163080"/>
-        <a:ext cx="6285600" cy="3211920"/>
+        <a:ext cx="6285240" cy="3211560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2173,9 +2270,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>480960</xdr:colOff>
+      <xdr:colOff>480600</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>128520</xdr:rowOff>
+      <xdr:rowOff>128160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2184,7 +2281,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5485680" y="162720"/>
-        <a:ext cx="5962320" cy="3054600"/>
+        <a:ext cx="5961960" cy="3054240"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2201,16 +2298,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>39960</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>474120</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>38160</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>548640</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>28800</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>778680</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>152640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2218,8 +2315,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5521320" y="38160"/>
-        <a:ext cx="6807240" cy="3241800"/>
+        <a:off x="7440120" y="0"/>
+        <a:ext cx="6806880" cy="3241440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2800,7 +2897,6 @@
       <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="0"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
@@ -2811,7 +2907,6 @@
       <c r="B2" s="4" t="n">
         <v>0.0108465551141083</v>
       </c>
-      <c r="C2" s="0"/>
       <c r="D2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2821,7 +2916,6 @@
       <c r="B3" s="4" t="n">
         <v>0.0226342666643933</v>
       </c>
-      <c r="C3" s="0"/>
       <c r="D3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2831,7 +2925,6 @@
       <c r="B4" s="4" t="n">
         <v>0.027455556100141</v>
       </c>
-      <c r="C4" s="0"/>
       <c r="D4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2841,7 +2934,6 @@
       <c r="B5" s="4" t="n">
         <v>0.0332052892550728</v>
       </c>
-      <c r="C5" s="0"/>
       <c r="D5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2851,7 +2943,6 @@
       <c r="B6" s="4" t="n">
         <v>0.034608729144128</v>
       </c>
-      <c r="C6" s="0"/>
       <c r="D6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2861,7 +2952,6 @@
       <c r="B7" s="4" t="n">
         <v>0.0415494509686245</v>
       </c>
-      <c r="C7" s="0"/>
       <c r="D7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2871,7 +2961,6 @@
       <c r="B8" s="4" t="n">
         <v>0.0460638599643128</v>
       </c>
-      <c r="C8" s="0"/>
       <c r="D8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2881,7 +2970,6 @@
       <c r="B9" s="3" t="n">
         <v>0.0463268620757961</v>
       </c>
-      <c r="C9" s="0"/>
       <c r="D9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2891,7 +2979,6 @@
       <c r="B10" s="4" t="n">
         <v>0.0599086107996893</v>
       </c>
-      <c r="C10" s="0"/>
       <c r="D10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2901,7 +2988,6 @@
       <c r="B11" s="4" t="n">
         <v>0.0629669593903209</v>
       </c>
-      <c r="C11" s="0"/>
       <c r="D11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2911,7 +2997,6 @@
       <c r="B12" s="4" t="n">
         <v>0.0711634580873181</v>
       </c>
-      <c r="C12" s="0"/>
       <c r="D12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2921,7 +3006,6 @@
       <c r="B13" s="4" t="n">
         <v>0.083912055247766</v>
       </c>
-      <c r="C13" s="0"/>
       <c r="D13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2931,7 +3015,6 @@
       <c r="B14" s="4" t="n">
         <v>0.131130033920739</v>
       </c>
-      <c r="C14" s="0"/>
       <c r="D14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2941,7 +3024,6 @@
       <c r="B15" s="4" t="n">
         <v>0.279014130933508</v>
       </c>
-      <c r="C15" s="0"/>
       <c r="D15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2951,7 +3033,6 @@
       <c r="B16" s="4" t="n">
         <v>0.396456691370473</v>
       </c>
-      <c r="C16" s="0"/>
       <c r="D16" s="4"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -3148,231 +3229,232 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>0.908138646571831</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>0.396456691370473</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>0.0932991636551523</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>0.732145359088816</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>0.279014130933508</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>0.058864187630119</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>0.418928020613512</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>0.131130033920739</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>0.0737053906193861</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>0.395130170015131</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>0.083912055247766</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0.0441173506620093</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>0.236012416163012</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>0.0711634580873181</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0.130435018511475</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>0.212571002672446</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0.0599086107996893</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0.136177451289278</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0.174985413000473</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>0.0629669593903209</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0.111690524931908</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>0.164664052820296</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>0.034608729144128</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0.121666608441389</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0.157541755617472</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>0.0463268620757961</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0.153283050739494</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>0.140363740121024</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>0.0415494509686245</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>4.11859599274385</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>0.137222644731534</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>0.027455556100141</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.285522869842013</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>0.119678415800646</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>0.0460638599643128</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0.228220963777834</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>0.112411016667618</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>0.0332052892550728</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>2.13081619568869</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>0.0914443287122927</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>0.0226342666643933</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0.795146019510512</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B16" s="7" t="n">
         <v>0.0441468721692524</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C16" s="7" t="n">
         <v>0.0108465551141083</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D16" s="7" t="n">
         <v>0.256016071870918</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>0.0914443287122927</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>0.0226342666643933</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0.795146019510512</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>0.112411016667618</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0.0332052892550728</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>2.13081619568869</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>0.119678415800646</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0.0460638599643128</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0.228220963777834</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>0.137222644731534</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0.027455556100141</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0.285522869842013</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>0.140363740121024</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0.0415494509686245</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>4.11859599274385</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>0.157541755617472</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0.0463268620757961</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0.153283050739494</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>0.164664052820296</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>0.034608729144128</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0.121666608441389</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>0.174985413000473</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0.0629669593903209</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0.111690524931908</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>0.212571002672446</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0.0599086107996893</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0.136177451289278</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>0.236012416163012</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0.0711634580873181</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0.130435018511475</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>0.395130170015131</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0.083912055247766</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0.0441173506620093</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>0.418928020613512</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>0.131130033920739</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>0.0737053906193861</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>0.732145359088816</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>0.279014130933508</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0.058864187630119</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>0.908138646571831</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>0.396456691370473</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>0.0932991636551523</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
